--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -722,16 +722,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>517800</v>
+        <v>526300</v>
       </c>
       <c r="E8" s="3">
-        <v>40800</v>
+        <v>41500</v>
       </c>
       <c r="F8" s="3">
-        <v>44300</v>
+        <v>45000</v>
       </c>
       <c r="G8" s="3">
-        <v>46200</v>
+        <v>47000</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -761,16 +761,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>405700</v>
+        <v>412400</v>
       </c>
       <c r="E9" s="3">
-        <v>36800</v>
+        <v>37400</v>
       </c>
       <c r="F9" s="3">
-        <v>37600</v>
+        <v>38200</v>
       </c>
       <c r="G9" s="3">
-        <v>34000</v>
+        <v>34500</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -800,16 +800,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>112000</v>
+        <v>113900</v>
       </c>
       <c r="E10" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="F10" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="G10" s="3">
-        <v>12200</v>
+        <v>12400</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -934,16 +934,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>149100</v>
+        <v>151500</v>
       </c>
       <c r="E14" s="3">
-        <v>64500</v>
+        <v>65500</v>
       </c>
       <c r="F14" s="3">
-        <v>91300</v>
+        <v>92800</v>
       </c>
       <c r="G14" s="3">
-        <v>100900</v>
+        <v>102600</v>
       </c>
       <c r="H14" s="3">
         <v>1300</v>
@@ -973,13 +973,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>29800</v>
+        <v>30300</v>
       </c>
       <c r="E15" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="F15" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G15" s="3">
         <v>400</v>
@@ -1026,22 +1026,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>783800</v>
+        <v>796700</v>
       </c>
       <c r="E17" s="3">
-        <v>160800</v>
+        <v>163500</v>
       </c>
       <c r="F17" s="3">
-        <v>181700</v>
+        <v>184700</v>
       </c>
       <c r="G17" s="3">
-        <v>134200</v>
+        <v>136500</v>
       </c>
       <c r="H17" s="3">
-        <v>20100</v>
+        <v>20500</v>
       </c>
       <c r="I17" s="3">
-        <v>9400</v>
+        <v>9500</v>
       </c>
       <c r="J17" s="3">
         <v>1100</v>
@@ -1065,16 +1065,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-266000</v>
+        <v>-270400</v>
       </c>
       <c r="E18" s="3">
-        <v>-120000</v>
+        <v>-122000</v>
       </c>
       <c r="F18" s="3">
-        <v>-137400</v>
+        <v>-139700</v>
       </c>
       <c r="G18" s="3">
-        <v>-88000</v>
+        <v>-89500</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1121,16 +1121,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="E20" s="3">
-        <v>-50000</v>
+        <v>-50900</v>
       </c>
       <c r="F20" s="3">
-        <v>-5900</v>
+        <v>-6000</v>
       </c>
       <c r="G20" s="3">
-        <v>-8000</v>
+        <v>-8100</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1160,16 +1160,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-237200</v>
+        <v>-241100</v>
       </c>
       <c r="E21" s="3">
-        <v>-162600</v>
+        <v>-165300</v>
       </c>
       <c r="F21" s="3">
-        <v>-134800</v>
+        <v>-137000</v>
       </c>
       <c r="G21" s="3">
-        <v>-88900</v>
+        <v>-90400</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1199,19 +1199,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="E22" s="3">
         <v>600</v>
       </c>
       <c r="F22" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="G22" s="3">
-        <v>10300</v>
+        <v>10500</v>
       </c>
       <c r="H22" s="3">
-        <v>20900</v>
+        <v>21300</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1238,22 +1238,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-276100</v>
+        <v>-280600</v>
       </c>
       <c r="E23" s="3">
-        <v>-170600</v>
+        <v>-173400</v>
       </c>
       <c r="F23" s="3">
-        <v>-150000</v>
+        <v>-152500</v>
       </c>
       <c r="G23" s="3">
-        <v>-106400</v>
+        <v>-108100</v>
       </c>
       <c r="H23" s="3">
-        <v>-41100</v>
+        <v>-41800</v>
       </c>
       <c r="I23" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="J23" s="3">
         <v>-1100</v>
@@ -1277,7 +1277,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-5300</v>
+        <v>-5400</v>
       </c>
       <c r="E24" s="3">
         <v>-5800</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1355,22 +1355,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-270800</v>
+        <v>-275200</v>
       </c>
       <c r="E26" s="3">
-        <v>-164900</v>
+        <v>-167600</v>
       </c>
       <c r="F26" s="3">
-        <v>-150000</v>
+        <v>-152500</v>
       </c>
       <c r="G26" s="3">
-        <v>-103700</v>
+        <v>-105500</v>
       </c>
       <c r="H26" s="3">
-        <v>-41100</v>
+        <v>-41800</v>
       </c>
       <c r="I26" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="J26" s="3">
         <v>-1100</v>
@@ -1394,22 +1394,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-243600</v>
+        <v>-247600</v>
       </c>
       <c r="E27" s="3">
-        <v>-165000</v>
+        <v>-167700</v>
       </c>
       <c r="F27" s="3">
-        <v>-145100</v>
+        <v>-147500</v>
       </c>
       <c r="G27" s="3">
-        <v>-103600</v>
+        <v>-105300</v>
       </c>
       <c r="H27" s="3">
-        <v>-41100</v>
+        <v>-41800</v>
       </c>
       <c r="I27" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="J27" s="3">
         <v>-1100</v>
@@ -1478,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-24400</v>
+        <v>-24900</v>
       </c>
       <c r="G29" s="3">
-        <v>-93700</v>
+        <v>-95300</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>3</v>
@@ -1589,16 +1589,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="E32" s="3">
-        <v>50000</v>
+        <v>50900</v>
       </c>
       <c r="F32" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="G32" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1628,22 +1628,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-243600</v>
+        <v>-247600</v>
       </c>
       <c r="E33" s="3">
-        <v>-165000</v>
+        <v>-167700</v>
       </c>
       <c r="F33" s="3">
-        <v>-169600</v>
+        <v>-172400</v>
       </c>
       <c r="G33" s="3">
-        <v>-197400</v>
+        <v>-200600</v>
       </c>
       <c r="H33" s="3">
-        <v>-41100</v>
+        <v>-41800</v>
       </c>
       <c r="I33" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="J33" s="3">
         <v>-1100</v>
@@ -1706,22 +1706,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-243600</v>
+        <v>-247600</v>
       </c>
       <c r="E35" s="3">
-        <v>-165000</v>
+        <v>-167700</v>
       </c>
       <c r="F35" s="3">
-        <v>-169600</v>
+        <v>-172400</v>
       </c>
       <c r="G35" s="3">
-        <v>-197400</v>
+        <v>-200600</v>
       </c>
       <c r="H35" s="3">
-        <v>-41100</v>
+        <v>-41800</v>
       </c>
       <c r="I35" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="J35" s="3">
         <v>-1100</v>
@@ -1823,22 +1823,22 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>203300</v>
+        <v>206600</v>
       </c>
       <c r="E41" s="3">
-        <v>405900</v>
+        <v>412500</v>
       </c>
       <c r="F41" s="3">
-        <v>43900</v>
+        <v>44600</v>
       </c>
       <c r="G41" s="3">
-        <v>33000</v>
+        <v>33500</v>
       </c>
       <c r="H41" s="3">
-        <v>10300</v>
+        <v>10400</v>
       </c>
       <c r="I41" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="J41" s="3">
         <v>2700</v>
@@ -1862,10 +1862,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>23400</v>
+        <v>23800</v>
       </c>
       <c r="E42" s="3">
-        <v>66000</v>
+        <v>67100</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1901,16 +1901,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16500</v>
+        <v>16700</v>
       </c>
       <c r="E43" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="F43" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G43" s="3">
-        <v>20100</v>
+        <v>20400</v>
       </c>
       <c r="H43" s="3">
         <v>2000</v>
@@ -1940,19 +1940,19 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>95400</v>
+        <v>97000</v>
       </c>
       <c r="E44" s="3">
-        <v>44300</v>
+        <v>45100</v>
       </c>
       <c r="F44" s="3">
-        <v>21200</v>
+        <v>21500</v>
       </c>
       <c r="G44" s="3">
-        <v>54000</v>
+        <v>54900</v>
       </c>
       <c r="H44" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I44" s="3">
         <v>300</v>
@@ -1979,16 +1979,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>26000</v>
+        <v>26500</v>
       </c>
       <c r="E45" s="3">
-        <v>25000</v>
+        <v>25400</v>
       </c>
       <c r="F45" s="3">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G45" s="3">
-        <v>18500</v>
+        <v>18800</v>
       </c>
       <c r="H45" s="3">
         <v>2000</v>
@@ -2018,25 +2018,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>364600</v>
+        <v>370600</v>
       </c>
       <c r="E46" s="3">
-        <v>529400</v>
+        <v>538100</v>
       </c>
       <c r="F46" s="3">
-        <v>86100</v>
+        <v>87500</v>
       </c>
       <c r="G46" s="3">
-        <v>125500</v>
+        <v>127600</v>
       </c>
       <c r="H46" s="3">
-        <v>15800</v>
+        <v>16000</v>
       </c>
       <c r="I46" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="J46" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2057,13 +2057,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>457700</v>
+        <v>465200</v>
       </c>
       <c r="E47" s="3">
-        <v>367800</v>
+        <v>373900</v>
       </c>
       <c r="F47" s="3">
-        <v>37700</v>
+        <v>38300</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -2096,25 +2096,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>201800</v>
+        <v>205100</v>
       </c>
       <c r="E48" s="3">
-        <v>45900</v>
+        <v>46700</v>
       </c>
       <c r="F48" s="3">
-        <v>85000</v>
+        <v>86400</v>
       </c>
       <c r="G48" s="3">
-        <v>205000</v>
+        <v>208400</v>
       </c>
       <c r="H48" s="3">
-        <v>64300</v>
+        <v>65400</v>
       </c>
       <c r="I48" s="3">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="J48" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2135,16 +2135,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>103300</v>
+        <v>105000</v>
       </c>
       <c r="E49" s="3">
-        <v>89200</v>
+        <v>90600</v>
       </c>
       <c r="F49" s="3">
         <v>3700</v>
       </c>
       <c r="G49" s="3">
-        <v>40300</v>
+        <v>41000</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -2252,10 +2252,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="E52" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="F52" s="3">
         <v>1900</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -2330,25 +2330,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1133700</v>
+        <v>1152300</v>
       </c>
       <c r="E54" s="3">
-        <v>1037900</v>
+        <v>1055000</v>
       </c>
       <c r="F54" s="3">
-        <v>214400</v>
+        <v>217900</v>
       </c>
       <c r="G54" s="3">
-        <v>370800</v>
+        <v>376900</v>
       </c>
       <c r="H54" s="3">
-        <v>80100</v>
+        <v>81400</v>
       </c>
       <c r="I54" s="3">
-        <v>18700</v>
+        <v>19000</v>
       </c>
       <c r="J54" s="3">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2403,19 +2403,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="E57" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="F57" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="G57" s="3">
-        <v>14700</v>
+        <v>14900</v>
       </c>
       <c r="H57" s="3">
-        <v>14000</v>
+        <v>14300</v>
       </c>
       <c r="I57" s="3">
         <v>3600</v>
@@ -2442,22 +2442,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22000</v>
+        <v>22300</v>
       </c>
       <c r="E58" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>129900</v>
+        <v>132000</v>
       </c>
       <c r="H58" s="3">
-        <v>36600</v>
+        <v>37200</v>
       </c>
       <c r="I58" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2481,16 +2481,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>35900</v>
+        <v>36500</v>
       </c>
       <c r="E59" s="3">
-        <v>40700</v>
+        <v>41400</v>
       </c>
       <c r="F59" s="3">
-        <v>13700</v>
+        <v>14000</v>
       </c>
       <c r="G59" s="3">
-        <v>51200</v>
+        <v>52000</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2520,22 +2520,22 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>65000</v>
+        <v>66000</v>
       </c>
       <c r="E60" s="3">
-        <v>47900</v>
+        <v>48700</v>
       </c>
       <c r="F60" s="3">
-        <v>17600</v>
+        <v>17800</v>
       </c>
       <c r="G60" s="3">
-        <v>195700</v>
+        <v>199000</v>
       </c>
       <c r="H60" s="3">
-        <v>50600</v>
+        <v>51500</v>
       </c>
       <c r="I60" s="3">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="J60" s="3">
         <v>800</v>
@@ -2559,19 +2559,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>101500</v>
+        <v>103200</v>
       </c>
       <c r="E61" s="3">
-        <v>20200</v>
+        <v>20500</v>
       </c>
       <c r="F61" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G61" s="3">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="H61" s="3">
-        <v>35200</v>
+        <v>35800</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2754,22 +2754,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>183800</v>
+        <v>186900</v>
       </c>
       <c r="E66" s="3">
-        <v>71500</v>
+        <v>72700</v>
       </c>
       <c r="F66" s="3">
-        <v>21500</v>
+        <v>21900</v>
       </c>
       <c r="G66" s="3">
-        <v>213400</v>
+        <v>216900</v>
       </c>
       <c r="H66" s="3">
-        <v>85900</v>
+        <v>87300</v>
       </c>
       <c r="I66" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="J66" s="3">
         <v>800</v>
@@ -2966,25 +2966,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-792300</v>
+        <v>-805300</v>
       </c>
       <c r="E72" s="3">
-        <v>-564900</v>
+        <v>-574200</v>
       </c>
       <c r="F72" s="3">
-        <v>-406000</v>
+        <v>-412700</v>
       </c>
       <c r="G72" s="3">
-        <v>-241700</v>
+        <v>-245700</v>
       </c>
       <c r="H72" s="3">
-        <v>-62400</v>
+        <v>-63400</v>
       </c>
       <c r="I72" s="3">
-        <v>-12100</v>
+        <v>-12300</v>
       </c>
       <c r="J72" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3122,25 +3122,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>949800</v>
+        <v>965500</v>
       </c>
       <c r="E76" s="3">
-        <v>966400</v>
+        <v>982300</v>
       </c>
       <c r="F76" s="3">
-        <v>192800</v>
+        <v>196000</v>
       </c>
       <c r="G76" s="3">
-        <v>157400</v>
+        <v>160000</v>
       </c>
       <c r="H76" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="I76" s="3">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="J76" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3244,22 +3244,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-243600</v>
+        <v>-247600</v>
       </c>
       <c r="E81" s="3">
-        <v>-165000</v>
+        <v>-167700</v>
       </c>
       <c r="F81" s="3">
-        <v>-169600</v>
+        <v>-172400</v>
       </c>
       <c r="G81" s="3">
-        <v>-197400</v>
+        <v>-200600</v>
       </c>
       <c r="H81" s="3">
-        <v>-41100</v>
+        <v>-41800</v>
       </c>
       <c r="I81" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="J81" s="3">
         <v>-1100</v>
@@ -3300,16 +3300,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>34400</v>
+        <v>35000</v>
       </c>
       <c r="E83" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="F83" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="G83" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -3534,22 +3534,22 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="E89" s="3">
-        <v>-113200</v>
+        <v>-115100</v>
       </c>
       <c r="F89" s="3">
-        <v>-41800</v>
+        <v>-42500</v>
       </c>
       <c r="G89" s="3">
-        <v>-82000</v>
+        <v>-83300</v>
       </c>
       <c r="H89" s="3">
-        <v>-18500</v>
+        <v>-18800</v>
       </c>
       <c r="I89" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="J89" s="3">
         <v>-1000</v>
@@ -3590,7 +3590,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7800</v>
+        <v>-7900</v>
       </c>
       <c r="E91" s="3">
         <v>-2800</v>
@@ -3599,13 +3599,13 @@
         <v>-2200</v>
       </c>
       <c r="G91" s="3">
-        <v>-100400</v>
+        <v>-102100</v>
       </c>
       <c r="H91" s="3">
-        <v>-55500</v>
+        <v>-56400</v>
       </c>
       <c r="I91" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="J91" s="3">
         <v>-3500</v>
@@ -3707,25 +3707,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-167300</v>
+        <v>-170100</v>
       </c>
       <c r="E94" s="3">
-        <v>-360800</v>
+        <v>-366700</v>
       </c>
       <c r="F94" s="3">
-        <v>-51500</v>
+        <v>-52400</v>
       </c>
       <c r="G94" s="3">
-        <v>-155000</v>
+        <v>-157500</v>
       </c>
       <c r="H94" s="3">
-        <v>-48000</v>
+        <v>-48800</v>
       </c>
       <c r="I94" s="3">
-        <v>-7000</v>
+        <v>-7200</v>
       </c>
       <c r="J94" s="3">
-        <v>-2800</v>
+        <v>-2900</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3919,25 +3919,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-30400</v>
+        <v>-30900</v>
       </c>
       <c r="E100" s="3">
-        <v>836000</v>
+        <v>849800</v>
       </c>
       <c r="F100" s="3">
-        <v>103800</v>
+        <v>105500</v>
       </c>
       <c r="G100" s="3">
-        <v>260500</v>
+        <v>264800</v>
       </c>
       <c r="H100" s="3">
-        <v>71200</v>
+        <v>72300</v>
       </c>
       <c r="I100" s="3">
-        <v>13700</v>
+        <v>14000</v>
       </c>
       <c r="J100" s="3">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3997,19 +3997,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-202600</v>
+        <v>-205900</v>
       </c>
       <c r="E102" s="3">
-        <v>362000</v>
+        <v>367900</v>
       </c>
       <c r="F102" s="3">
-        <v>10900</v>
+        <v>11100</v>
       </c>
       <c r="G102" s="3">
-        <v>22700</v>
+        <v>23100</v>
       </c>
       <c r="H102" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="I102" s="3">
         <v>2900</v>

--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>SNDL</t>
   </si>
@@ -656,56 +656,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43159</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42794</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,26 +715,29 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>526300</v>
+        <v>662400</v>
       </c>
       <c r="E8" s="3">
-        <v>41500</v>
+        <v>519000</v>
       </c>
       <c r="F8" s="3">
-        <v>45000</v>
+        <v>40900</v>
       </c>
       <c r="G8" s="3">
-        <v>47000</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+        <v>44400</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46300</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -751,29 +754,32 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>412400</v>
+        <v>502400</v>
       </c>
       <c r="E9" s="3">
-        <v>37400</v>
+        <v>406700</v>
       </c>
       <c r="F9" s="3">
-        <v>38200</v>
+        <v>36900</v>
       </c>
       <c r="G9" s="3">
-        <v>34500</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+        <v>37700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>34000</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -793,26 +799,29 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>113900</v>
+        <v>160100</v>
       </c>
       <c r="E10" s="3">
-        <v>4100</v>
+        <v>112300</v>
       </c>
       <c r="F10" s="3">
-        <v>6800</v>
+        <v>4000</v>
       </c>
       <c r="G10" s="3">
-        <v>12400</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+        <v>6700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>12300</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -832,9 +841,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,32 +862,33 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
         <v>1800</v>
       </c>
       <c r="F12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,9 +901,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,35 +943,38 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>151500</v>
+        <v>85100</v>
       </c>
       <c r="E14" s="3">
-        <v>65500</v>
+        <v>149400</v>
       </c>
       <c r="F14" s="3">
-        <v>92800</v>
+        <v>64600</v>
       </c>
       <c r="G14" s="3">
-        <v>102600</v>
+        <v>91500</v>
       </c>
       <c r="H14" s="3">
-        <v>1300</v>
+        <v>101200</v>
       </c>
       <c r="I14" s="3">
         <v>1300</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -966,36 +985,39 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>30300</v>
+        <v>43900</v>
       </c>
       <c r="E15" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="F15" s="3">
-        <v>3500</v>
-      </c>
       <c r="G15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H15" s="3">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1005,9 +1027,12 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,35 +1045,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>796700</v>
+        <v>794400</v>
       </c>
       <c r="E17" s="3">
-        <v>163500</v>
+        <v>785600</v>
       </c>
       <c r="F17" s="3">
-        <v>184700</v>
+        <v>161200</v>
       </c>
       <c r="G17" s="3">
-        <v>136500</v>
+        <v>182100</v>
       </c>
       <c r="H17" s="3">
-        <v>20500</v>
+        <v>134600</v>
       </c>
       <c r="I17" s="3">
-        <v>9500</v>
+        <v>20200</v>
       </c>
       <c r="J17" s="3">
+        <v>9400</v>
+      </c>
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1058,26 +1084,29 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-270400</v>
+        <v>-131900</v>
       </c>
       <c r="E18" s="3">
-        <v>-122000</v>
+        <v>-266600</v>
       </c>
       <c r="F18" s="3">
-        <v>-139700</v>
+        <v>-120300</v>
       </c>
       <c r="G18" s="3">
-        <v>-89500</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>-137700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-88200</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1097,9 +1126,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,25 +1147,26 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-50200</v>
+      </c>
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="E20" s="3">
-        <v>-50900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-8000</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1153,26 +1186,29 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-241100</v>
+        <v>-72400</v>
       </c>
       <c r="E21" s="3">
-        <v>-165300</v>
+        <v>-238100</v>
       </c>
       <c r="F21" s="3">
-        <v>-137000</v>
+        <v>-163100</v>
       </c>
       <c r="G21" s="3">
-        <v>-90400</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>-135200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-89200</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1192,35 +1228,38 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="E22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6800</v>
       </c>
-      <c r="G22" s="3">
-        <v>10500</v>
-      </c>
       <c r="H22" s="3">
-        <v>21300</v>
+        <v>10400</v>
       </c>
       <c r="I22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1231,36 +1270,39 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-280600</v>
+        <v>-125400</v>
       </c>
       <c r="E23" s="3">
-        <v>-173400</v>
+        <v>-276800</v>
       </c>
       <c r="F23" s="3">
-        <v>-152500</v>
+        <v>-171000</v>
       </c>
       <c r="G23" s="3">
-        <v>-108100</v>
+        <v>-150400</v>
       </c>
       <c r="H23" s="3">
-        <v>-41800</v>
+        <v>-106600</v>
       </c>
       <c r="I23" s="3">
-        <v>-9600</v>
+        <v>-41200</v>
       </c>
       <c r="J23" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,26 +1312,29 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5800</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-2600</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1306,12 +1351,15 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,36 +1396,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-275200</v>
+        <v>-125400</v>
       </c>
       <c r="E26" s="3">
-        <v>-167600</v>
+        <v>-271400</v>
       </c>
       <c r="F26" s="3">
-        <v>-152500</v>
+        <v>-165300</v>
       </c>
       <c r="G26" s="3">
-        <v>-105500</v>
+        <v>-150400</v>
       </c>
       <c r="H26" s="3">
-        <v>-41800</v>
+        <v>-104000</v>
       </c>
       <c r="I26" s="3">
-        <v>-9600</v>
+        <v>-41200</v>
       </c>
       <c r="J26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1387,36 +1438,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-247600</v>
+        <v>-122500</v>
       </c>
       <c r="E27" s="3">
-        <v>-167700</v>
+        <v>-244200</v>
       </c>
       <c r="F27" s="3">
-        <v>-147500</v>
+        <v>-165400</v>
       </c>
       <c r="G27" s="3">
-        <v>-105300</v>
+        <v>-145500</v>
       </c>
       <c r="H27" s="3">
-        <v>-41800</v>
+        <v>-103900</v>
       </c>
       <c r="I27" s="3">
-        <v>-9600</v>
+        <v>-41200</v>
       </c>
       <c r="J27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,9 +1480,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,26 +1522,29 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-24900</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-95300</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
+        <v>-24500</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-94000</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>3</v>
@@ -1498,15 +1558,18 @@
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,26 +1648,29 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F32" s="3">
+        <v>50200</v>
+      </c>
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="E32" s="3">
-        <v>50900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>8100</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>8000</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1621,36 +1690,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-247600</v>
+        <v>-125800</v>
       </c>
       <c r="E33" s="3">
-        <v>-167700</v>
+        <v>-244200</v>
       </c>
       <c r="F33" s="3">
-        <v>-172400</v>
+        <v>-165400</v>
       </c>
       <c r="G33" s="3">
-        <v>-200600</v>
+        <v>-170000</v>
       </c>
       <c r="H33" s="3">
-        <v>-41800</v>
+        <v>-197800</v>
       </c>
       <c r="I33" s="3">
-        <v>-9600</v>
+        <v>-41200</v>
       </c>
       <c r="J33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,9 +1732,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,36 +1774,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-247600</v>
+        <v>-125800</v>
       </c>
       <c r="E35" s="3">
-        <v>-167700</v>
+        <v>-244200</v>
       </c>
       <c r="F35" s="3">
-        <v>-172400</v>
+        <v>-165400</v>
       </c>
       <c r="G35" s="3">
-        <v>-200600</v>
+        <v>-170000</v>
       </c>
       <c r="H35" s="3">
-        <v>-41800</v>
+        <v>-197800</v>
       </c>
       <c r="I35" s="3">
-        <v>-9600</v>
+        <v>-41200</v>
       </c>
       <c r="J35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,41 +1816,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43159</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42794</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1782,9 +1863,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,35 +1902,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>206600</v>
+        <v>142100</v>
       </c>
       <c r="E41" s="3">
-        <v>412500</v>
+        <v>203800</v>
       </c>
       <c r="F41" s="3">
-        <v>44600</v>
+        <v>406800</v>
       </c>
       <c r="G41" s="3">
-        <v>33500</v>
+        <v>44000</v>
       </c>
       <c r="H41" s="3">
-        <v>10400</v>
+        <v>33000</v>
       </c>
       <c r="I41" s="3">
-        <v>5700</v>
+        <v>10300</v>
       </c>
       <c r="J41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K41" s="3">
         <v>2700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,20 +1941,23 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>23800</v>
+        <v>4800</v>
       </c>
       <c r="E42" s="3">
-        <v>67100</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>23500</v>
+      </c>
+      <c r="F42" s="3">
+        <v>66200</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1885,8 +1974,8 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1894,36 +1983,39 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16700</v>
+        <v>19700</v>
       </c>
       <c r="E43" s="3">
-        <v>8000</v>
+        <v>16500</v>
       </c>
       <c r="F43" s="3">
-        <v>11700</v>
+        <v>7900</v>
       </c>
       <c r="G43" s="3">
-        <v>20400</v>
+        <v>11600</v>
       </c>
       <c r="H43" s="3">
+        <v>20100</v>
+      </c>
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1933,35 +2025,38 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>97000</v>
+        <v>94400</v>
       </c>
       <c r="E44" s="3">
-        <v>45100</v>
+        <v>95700</v>
       </c>
       <c r="F44" s="3">
-        <v>21500</v>
+        <v>44400</v>
       </c>
       <c r="G44" s="3">
-        <v>54900</v>
+        <v>21200</v>
       </c>
       <c r="H44" s="3">
-        <v>1600</v>
+        <v>54100</v>
       </c>
       <c r="I44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -1972,36 +2067,39 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>26500</v>
+        <v>35500</v>
       </c>
       <c r="E45" s="3">
-        <v>25400</v>
+        <v>26100</v>
       </c>
       <c r="F45" s="3">
-        <v>9600</v>
+        <v>25000</v>
       </c>
       <c r="G45" s="3">
-        <v>18800</v>
+        <v>9400</v>
       </c>
       <c r="H45" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2011,36 +2109,39 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>370600</v>
+        <v>296500</v>
       </c>
       <c r="E46" s="3">
-        <v>538100</v>
+        <v>365500</v>
       </c>
       <c r="F46" s="3">
-        <v>87500</v>
+        <v>530700</v>
       </c>
       <c r="G46" s="3">
-        <v>127600</v>
+        <v>86300</v>
       </c>
       <c r="H46" s="3">
-        <v>16000</v>
+        <v>125800</v>
       </c>
       <c r="I46" s="3">
-        <v>6600</v>
+        <v>15800</v>
       </c>
       <c r="J46" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K46" s="3">
         <v>3100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,23 +2151,26 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>465200</v>
+        <v>427300</v>
       </c>
       <c r="E47" s="3">
-        <v>373900</v>
+        <v>458800</v>
       </c>
       <c r="F47" s="3">
-        <v>38300</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+        <v>368700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>37800</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2083,42 +2187,45 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>205100</v>
+        <v>205900</v>
       </c>
       <c r="E48" s="3">
-        <v>46700</v>
+        <v>202300</v>
       </c>
       <c r="F48" s="3">
-        <v>86400</v>
+        <v>46000</v>
       </c>
       <c r="G48" s="3">
-        <v>208400</v>
+        <v>85200</v>
       </c>
       <c r="H48" s="3">
-        <v>65400</v>
+        <v>205500</v>
       </c>
       <c r="I48" s="3">
-        <v>9700</v>
+        <v>64500</v>
       </c>
       <c r="J48" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K48" s="3">
         <v>5900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2128,35 +2235,38 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>105000</v>
+        <v>140200</v>
       </c>
       <c r="E49" s="3">
-        <v>90600</v>
+        <v>103600</v>
       </c>
       <c r="F49" s="3">
+        <v>89400</v>
+      </c>
+      <c r="G49" s="3">
         <v>3700</v>
       </c>
-      <c r="G49" s="3">
-        <v>41000</v>
-      </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>40400</v>
       </c>
       <c r="I49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>400</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>400</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2167,9 +2277,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,35 +2361,38 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E52" s="3">
         <v>6300</v>
       </c>
-      <c r="E52" s="3">
-        <v>5700</v>
-      </c>
       <c r="F52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G52" s="3">
         <v>1900</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+        <v>2300</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2284,9 +2403,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,36 +2445,39 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1152300</v>
+        <v>1073600</v>
       </c>
       <c r="E54" s="3">
-        <v>1055000</v>
+        <v>1136400</v>
       </c>
       <c r="F54" s="3">
-        <v>217900</v>
+        <v>1040400</v>
       </c>
       <c r="G54" s="3">
-        <v>376900</v>
+        <v>214900</v>
       </c>
       <c r="H54" s="3">
-        <v>81400</v>
+        <v>371700</v>
       </c>
       <c r="I54" s="3">
-        <v>19000</v>
+        <v>80300</v>
       </c>
       <c r="J54" s="3">
+        <v>18800</v>
+      </c>
+      <c r="K54" s="3">
         <v>9400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,9 +2487,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,35 +2526,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7200</v>
+        <v>16100</v>
       </c>
       <c r="E57" s="3">
-        <v>3100</v>
+        <v>7100</v>
       </c>
       <c r="F57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H57" s="3">
+        <v>14700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
-        <v>14900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>14300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,9 +2565,12 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2445,25 +2578,25 @@
         <v>22300</v>
       </c>
       <c r="E58" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
-        <v>132000</v>
-      </c>
       <c r="H58" s="3">
-        <v>37200</v>
+        <v>130200</v>
       </c>
       <c r="I58" s="3">
-        <v>5200</v>
+        <v>36700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+        <v>5100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2474,26 +2607,29 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>36500</v>
+        <v>36900</v>
       </c>
       <c r="E59" s="3">
-        <v>41400</v>
+        <v>36000</v>
       </c>
       <c r="F59" s="3">
-        <v>14000</v>
+        <v>40800</v>
       </c>
       <c r="G59" s="3">
-        <v>52000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+        <v>13800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>51300</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2510,39 +2646,42 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>66000</v>
+        <v>75200</v>
       </c>
       <c r="E60" s="3">
-        <v>48700</v>
+        <v>65100</v>
       </c>
       <c r="F60" s="3">
-        <v>17800</v>
+        <v>48000</v>
       </c>
       <c r="G60" s="3">
-        <v>199000</v>
+        <v>17600</v>
       </c>
       <c r="H60" s="3">
-        <v>51500</v>
+        <v>196200</v>
       </c>
       <c r="I60" s="3">
-        <v>8800</v>
+        <v>50800</v>
       </c>
       <c r="J60" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2552,33 +2691,36 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>103200</v>
+        <v>99500</v>
       </c>
       <c r="E61" s="3">
-        <v>20500</v>
+        <v>101800</v>
       </c>
       <c r="F61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
-        <v>12000</v>
-      </c>
       <c r="H61" s="3">
-        <v>35800</v>
+        <v>11800</v>
       </c>
       <c r="I61" s="3">
+        <v>35300</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2591,27 +2733,30 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3300</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2627,12 +2772,15 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,36 +2901,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>186900</v>
+        <v>190300</v>
       </c>
       <c r="E66" s="3">
-        <v>72700</v>
+        <v>184300</v>
       </c>
       <c r="F66" s="3">
-        <v>21900</v>
+        <v>71700</v>
       </c>
       <c r="G66" s="3">
-        <v>216900</v>
+        <v>21600</v>
       </c>
       <c r="H66" s="3">
-        <v>87300</v>
+        <v>213900</v>
       </c>
       <c r="I66" s="3">
-        <v>8900</v>
+        <v>86100</v>
       </c>
       <c r="J66" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K66" s="3">
         <v>800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2786,9 +2943,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,9 +3045,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,36 +3129,39 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-805300</v>
+        <v>-917200</v>
       </c>
       <c r="E72" s="3">
-        <v>-574200</v>
+        <v>-794200</v>
       </c>
       <c r="F72" s="3">
-        <v>-412700</v>
+        <v>-566300</v>
       </c>
       <c r="G72" s="3">
-        <v>-245700</v>
+        <v>-407000</v>
       </c>
       <c r="H72" s="3">
-        <v>-63400</v>
+        <v>-242300</v>
       </c>
       <c r="I72" s="3">
-        <v>-12300</v>
+        <v>-62500</v>
       </c>
       <c r="J72" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="K72" s="3">
         <v>-2700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,9 +3171,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,36 +3297,39 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>965500</v>
+        <v>883300</v>
       </c>
       <c r="E76" s="3">
-        <v>982300</v>
+        <v>952100</v>
       </c>
       <c r="F76" s="3">
-        <v>196000</v>
+        <v>968700</v>
       </c>
       <c r="G76" s="3">
-        <v>160000</v>
+        <v>193300</v>
       </c>
       <c r="H76" s="3">
+        <v>157800</v>
+      </c>
+      <c r="I76" s="3">
         <v>-5800</v>
       </c>
-      <c r="I76" s="3">
-        <v>10100</v>
-      </c>
       <c r="J76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K76" s="3">
         <v>8500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,9 +3339,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,41 +3381,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43159</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42794</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3237,36 +3428,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-247600</v>
+        <v>-125800</v>
       </c>
       <c r="E81" s="3">
-        <v>-167700</v>
+        <v>-244200</v>
       </c>
       <c r="F81" s="3">
-        <v>-172400</v>
+        <v>-165400</v>
       </c>
       <c r="G81" s="3">
-        <v>-200600</v>
+        <v>-170000</v>
       </c>
       <c r="H81" s="3">
-        <v>-41800</v>
+        <v>-197800</v>
       </c>
       <c r="I81" s="3">
-        <v>-9600</v>
+        <v>-41200</v>
       </c>
       <c r="J81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,9 +3470,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,35 +3491,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>35000</v>
+        <v>47300</v>
       </c>
       <c r="E83" s="3">
-        <v>7500</v>
+        <v>34500</v>
       </c>
       <c r="F83" s="3">
-        <v>8600</v>
+        <v>7400</v>
       </c>
       <c r="G83" s="3">
-        <v>7200</v>
+        <v>8400</v>
       </c>
       <c r="H83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3332,9 +3530,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,36 +3740,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-5000</v>
+        <v>-12100</v>
       </c>
       <c r="E89" s="3">
-        <v>-115100</v>
+        <v>-4900</v>
       </c>
       <c r="F89" s="3">
-        <v>-42500</v>
+        <v>-113500</v>
       </c>
       <c r="G89" s="3">
-        <v>-83300</v>
+        <v>-41900</v>
       </c>
       <c r="H89" s="3">
-        <v>-18800</v>
+        <v>-82200</v>
       </c>
       <c r="I89" s="3">
-        <v>-3900</v>
+        <v>-18500</v>
       </c>
       <c r="J89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3566,9 +3782,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,35 +3803,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7900</v>
+        <v>-5700</v>
       </c>
       <c r="E91" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-102100</v>
-      </c>
       <c r="H91" s="3">
-        <v>-56400</v>
+        <v>-100700</v>
       </c>
       <c r="I91" s="3">
-        <v>-5600</v>
+        <v>-55600</v>
       </c>
       <c r="J91" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,9 +3842,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,36 +3926,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-170100</v>
+        <v>-18100</v>
       </c>
       <c r="E94" s="3">
-        <v>-366700</v>
+        <v>-167700</v>
       </c>
       <c r="F94" s="3">
-        <v>-52400</v>
+        <v>-361700</v>
       </c>
       <c r="G94" s="3">
-        <v>-157500</v>
+        <v>-51700</v>
       </c>
       <c r="H94" s="3">
-        <v>-48800</v>
+        <v>-155300</v>
       </c>
       <c r="I94" s="3">
-        <v>-7200</v>
+        <v>-48100</v>
       </c>
       <c r="J94" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,9 +3968,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,8 +3989,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3795,9 +4028,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,36 +4154,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-30900</v>
+        <v>-31400</v>
       </c>
       <c r="E100" s="3">
-        <v>849800</v>
+        <v>-30500</v>
       </c>
       <c r="F100" s="3">
-        <v>105500</v>
+        <v>838000</v>
       </c>
       <c r="G100" s="3">
-        <v>264800</v>
+        <v>104000</v>
       </c>
       <c r="H100" s="3">
-        <v>72300</v>
+        <v>261100</v>
       </c>
       <c r="I100" s="3">
-        <v>14000</v>
+        <v>71300</v>
       </c>
       <c r="J100" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K100" s="3">
         <v>6500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,27 +4196,30 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3987,39 +4235,42 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-205900</v>
+        <v>-61600</v>
       </c>
       <c r="E102" s="3">
-        <v>367900</v>
+        <v>-203100</v>
       </c>
       <c r="F102" s="3">
-        <v>11100</v>
+        <v>362800</v>
       </c>
       <c r="G102" s="3">
-        <v>23100</v>
+        <v>11000</v>
       </c>
       <c r="H102" s="3">
-        <v>4800</v>
+        <v>22700</v>
       </c>
       <c r="I102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2500</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4029,7 +4280,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -725,19 +725,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>662400</v>
+        <v>669100</v>
       </c>
       <c r="E8" s="3">
-        <v>519000</v>
+        <v>524300</v>
       </c>
       <c r="F8" s="3">
-        <v>40900</v>
+        <v>41300</v>
       </c>
       <c r="G8" s="3">
-        <v>44400</v>
+        <v>44800</v>
       </c>
       <c r="H8" s="3">
-        <v>46300</v>
+        <v>46800</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -767,19 +767,19 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>502400</v>
+        <v>507400</v>
       </c>
       <c r="E9" s="3">
-        <v>406700</v>
+        <v>410800</v>
       </c>
       <c r="F9" s="3">
-        <v>36900</v>
+        <v>37300</v>
       </c>
       <c r="G9" s="3">
-        <v>37700</v>
+        <v>38100</v>
       </c>
       <c r="H9" s="3">
-        <v>34000</v>
+        <v>34400</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -809,19 +809,19 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>160100</v>
+        <v>161700</v>
       </c>
       <c r="E10" s="3">
-        <v>112300</v>
+        <v>113400</v>
       </c>
       <c r="F10" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="G10" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="H10" s="3">
-        <v>12300</v>
+        <v>12400</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -953,19 +953,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>85100</v>
+        <v>86000</v>
       </c>
       <c r="E14" s="3">
-        <v>149400</v>
+        <v>150900</v>
       </c>
       <c r="F14" s="3">
-        <v>64600</v>
+        <v>65300</v>
       </c>
       <c r="G14" s="3">
-        <v>91500</v>
+        <v>92500</v>
       </c>
       <c r="H14" s="3">
-        <v>101200</v>
+        <v>102200</v>
       </c>
       <c r="I14" s="3">
         <v>1300</v>
@@ -995,16 +995,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>43900</v>
+        <v>44300</v>
       </c>
       <c r="E15" s="3">
-        <v>29800</v>
+        <v>30100</v>
       </c>
       <c r="F15" s="3">
         <v>3900</v>
       </c>
       <c r="G15" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H15" s="3">
         <v>400</v>
@@ -1052,25 +1052,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>794400</v>
+        <v>802400</v>
       </c>
       <c r="E17" s="3">
-        <v>785600</v>
+        <v>793600</v>
       </c>
       <c r="F17" s="3">
-        <v>161200</v>
+        <v>162800</v>
       </c>
       <c r="G17" s="3">
-        <v>182100</v>
+        <v>184000</v>
       </c>
       <c r="H17" s="3">
-        <v>134600</v>
+        <v>135900</v>
       </c>
       <c r="I17" s="3">
-        <v>20200</v>
+        <v>20400</v>
       </c>
       <c r="J17" s="3">
-        <v>9400</v>
+        <v>9500</v>
       </c>
       <c r="K17" s="3">
         <v>1100</v>
@@ -1094,19 +1094,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-131900</v>
+        <v>-133300</v>
       </c>
       <c r="E18" s="3">
-        <v>-266600</v>
+        <v>-269300</v>
       </c>
       <c r="F18" s="3">
-        <v>-120300</v>
+        <v>-121500</v>
       </c>
       <c r="G18" s="3">
-        <v>-137700</v>
+        <v>-139100</v>
       </c>
       <c r="H18" s="3">
-        <v>-88200</v>
+        <v>-89100</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1154,19 +1154,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="E20" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="F20" s="3">
-        <v>-50200</v>
+        <v>-50700</v>
       </c>
       <c r="G20" s="3">
         <v>-5900</v>
       </c>
       <c r="H20" s="3">
-        <v>-8000</v>
+        <v>-8100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1196,19 +1196,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-72400</v>
+        <v>-73000</v>
       </c>
       <c r="E21" s="3">
-        <v>-238100</v>
+        <v>-240400</v>
       </c>
       <c r="F21" s="3">
-        <v>-163100</v>
+        <v>-164700</v>
       </c>
       <c r="G21" s="3">
-        <v>-135200</v>
+        <v>-136500</v>
       </c>
       <c r="H21" s="3">
-        <v>-89200</v>
+        <v>-90000</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1250,10 +1250,10 @@
         <v>6800</v>
       </c>
       <c r="H22" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="I22" s="3">
-        <v>21000</v>
+        <v>21200</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1280,25 +1280,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-125400</v>
+        <v>-126600</v>
       </c>
       <c r="E23" s="3">
-        <v>-276800</v>
+        <v>-279600</v>
       </c>
       <c r="F23" s="3">
-        <v>-171000</v>
+        <v>-172800</v>
       </c>
       <c r="G23" s="3">
-        <v>-150400</v>
+        <v>-151900</v>
       </c>
       <c r="H23" s="3">
-        <v>-106600</v>
+        <v>-107700</v>
       </c>
       <c r="I23" s="3">
-        <v>-41200</v>
+        <v>-41600</v>
       </c>
       <c r="J23" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="K23" s="3">
         <v>-1100</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1406,25 +1406,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-125400</v>
+        <v>-126600</v>
       </c>
       <c r="E26" s="3">
-        <v>-271400</v>
+        <v>-274100</v>
       </c>
       <c r="F26" s="3">
-        <v>-165300</v>
+        <v>-166900</v>
       </c>
       <c r="G26" s="3">
-        <v>-150400</v>
+        <v>-151900</v>
       </c>
       <c r="H26" s="3">
-        <v>-104000</v>
+        <v>-105000</v>
       </c>
       <c r="I26" s="3">
-        <v>-41200</v>
+        <v>-41600</v>
       </c>
       <c r="J26" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="K26" s="3">
         <v>-1100</v>
@@ -1448,25 +1448,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-122500</v>
+        <v>-123800</v>
       </c>
       <c r="E27" s="3">
-        <v>-244200</v>
+        <v>-246700</v>
       </c>
       <c r="F27" s="3">
-        <v>-165400</v>
+        <v>-167100</v>
       </c>
       <c r="G27" s="3">
-        <v>-145500</v>
+        <v>-146900</v>
       </c>
       <c r="H27" s="3">
-        <v>-103900</v>
+        <v>-104900</v>
       </c>
       <c r="I27" s="3">
-        <v>-41200</v>
+        <v>-41600</v>
       </c>
       <c r="J27" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="K27" s="3">
         <v>-1100</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-24500</v>
+        <v>-24800</v>
       </c>
       <c r="H29" s="3">
-        <v>-94000</v>
+        <v>-94900</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>3</v>
@@ -1658,19 +1658,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12400</v>
+        <v>-12500</v>
       </c>
       <c r="E32" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="F32" s="3">
-        <v>50200</v>
+        <v>50700</v>
       </c>
       <c r="G32" s="3">
         <v>5900</v>
       </c>
       <c r="H32" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1700,25 +1700,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-125800</v>
+        <v>-127100</v>
       </c>
       <c r="E33" s="3">
-        <v>-244200</v>
+        <v>-246700</v>
       </c>
       <c r="F33" s="3">
-        <v>-165400</v>
+        <v>-167100</v>
       </c>
       <c r="G33" s="3">
-        <v>-170000</v>
+        <v>-171700</v>
       </c>
       <c r="H33" s="3">
-        <v>-197800</v>
+        <v>-199800</v>
       </c>
       <c r="I33" s="3">
-        <v>-41200</v>
+        <v>-41600</v>
       </c>
       <c r="J33" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="K33" s="3">
         <v>-1100</v>
@@ -1784,25 +1784,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-125800</v>
+        <v>-127100</v>
       </c>
       <c r="E35" s="3">
-        <v>-244200</v>
+        <v>-246700</v>
       </c>
       <c r="F35" s="3">
-        <v>-165400</v>
+        <v>-167100</v>
       </c>
       <c r="G35" s="3">
-        <v>-170000</v>
+        <v>-171700</v>
       </c>
       <c r="H35" s="3">
-        <v>-197800</v>
+        <v>-199800</v>
       </c>
       <c r="I35" s="3">
-        <v>-41200</v>
+        <v>-41600</v>
       </c>
       <c r="J35" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="K35" s="3">
         <v>-1100</v>
@@ -1909,25 +1909,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>142100</v>
+        <v>143600</v>
       </c>
       <c r="E41" s="3">
-        <v>203800</v>
+        <v>205800</v>
       </c>
       <c r="F41" s="3">
-        <v>406800</v>
+        <v>410900</v>
       </c>
       <c r="G41" s="3">
-        <v>44000</v>
+        <v>44400</v>
       </c>
       <c r="H41" s="3">
-        <v>33000</v>
+        <v>33400</v>
       </c>
       <c r="I41" s="3">
-        <v>10300</v>
+        <v>10400</v>
       </c>
       <c r="J41" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="K41" s="3">
         <v>2700</v>
@@ -1951,13 +1951,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="E42" s="3">
-        <v>23500</v>
+        <v>23700</v>
       </c>
       <c r="F42" s="3">
-        <v>66200</v>
+        <v>66800</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1993,19 +1993,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>19700</v>
+        <v>19900</v>
       </c>
       <c r="E43" s="3">
-        <v>16500</v>
+        <v>16700</v>
       </c>
       <c r="F43" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="G43" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="H43" s="3">
-        <v>20100</v>
+        <v>20300</v>
       </c>
       <c r="I43" s="3">
         <v>2000</v>
@@ -2035,22 +2035,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>94400</v>
+        <v>95300</v>
       </c>
       <c r="E44" s="3">
-        <v>95700</v>
+        <v>96600</v>
       </c>
       <c r="F44" s="3">
-        <v>44400</v>
+        <v>44900</v>
       </c>
       <c r="G44" s="3">
-        <v>21200</v>
+        <v>21500</v>
       </c>
       <c r="H44" s="3">
-        <v>54100</v>
+        <v>54700</v>
       </c>
       <c r="I44" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
@@ -2077,19 +2077,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>35500</v>
+        <v>35900</v>
       </c>
       <c r="E45" s="3">
-        <v>26100</v>
+        <v>26400</v>
       </c>
       <c r="F45" s="3">
-        <v>25000</v>
+        <v>25300</v>
       </c>
       <c r="G45" s="3">
-        <v>9400</v>
+        <v>9500</v>
       </c>
       <c r="H45" s="3">
-        <v>18500</v>
+        <v>18700</v>
       </c>
       <c r="I45" s="3">
         <v>2000</v>
@@ -2119,25 +2119,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>296500</v>
+        <v>299500</v>
       </c>
       <c r="E46" s="3">
-        <v>365500</v>
+        <v>369100</v>
       </c>
       <c r="F46" s="3">
-        <v>530700</v>
+        <v>536000</v>
       </c>
       <c r="G46" s="3">
-        <v>86300</v>
+        <v>87100</v>
       </c>
       <c r="H46" s="3">
-        <v>125800</v>
+        <v>127100</v>
       </c>
       <c r="I46" s="3">
-        <v>15800</v>
+        <v>16000</v>
       </c>
       <c r="J46" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="K46" s="3">
         <v>3100</v>
@@ -2161,16 +2161,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>427300</v>
+        <v>431600</v>
       </c>
       <c r="E47" s="3">
-        <v>458800</v>
+        <v>463400</v>
       </c>
       <c r="F47" s="3">
-        <v>368700</v>
+        <v>372400</v>
       </c>
       <c r="G47" s="3">
-        <v>37800</v>
+        <v>38200</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2203,22 +2203,22 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>205900</v>
+        <v>208000</v>
       </c>
       <c r="E48" s="3">
-        <v>202300</v>
+        <v>204300</v>
       </c>
       <c r="F48" s="3">
-        <v>46000</v>
+        <v>46500</v>
       </c>
       <c r="G48" s="3">
-        <v>85200</v>
+        <v>86100</v>
       </c>
       <c r="H48" s="3">
-        <v>205500</v>
+        <v>207600</v>
       </c>
       <c r="I48" s="3">
-        <v>64500</v>
+        <v>65100</v>
       </c>
       <c r="J48" s="3">
         <v>9600</v>
@@ -2245,19 +2245,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>140200</v>
+        <v>141700</v>
       </c>
       <c r="E49" s="3">
-        <v>103600</v>
+        <v>104600</v>
       </c>
       <c r="F49" s="3">
-        <v>89400</v>
+        <v>90300</v>
       </c>
       <c r="G49" s="3">
         <v>3700</v>
       </c>
       <c r="H49" s="3">
-        <v>40400</v>
+        <v>40800</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2371,13 +2371,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="E52" s="3">
         <v>6300</v>
       </c>
       <c r="F52" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="G52" s="3">
         <v>1900</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2455,25 +2455,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1073600</v>
+        <v>1084400</v>
       </c>
       <c r="E54" s="3">
-        <v>1136400</v>
+        <v>1147900</v>
       </c>
       <c r="F54" s="3">
-        <v>1040400</v>
+        <v>1050900</v>
       </c>
       <c r="G54" s="3">
-        <v>214900</v>
+        <v>217100</v>
       </c>
       <c r="H54" s="3">
-        <v>371700</v>
+        <v>375400</v>
       </c>
       <c r="I54" s="3">
-        <v>80300</v>
+        <v>81100</v>
       </c>
       <c r="J54" s="3">
-        <v>18800</v>
+        <v>19000</v>
       </c>
       <c r="K54" s="3">
         <v>9400</v>
@@ -2533,22 +2533,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>16100</v>
+        <v>16200</v>
       </c>
       <c r="E57" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="F57" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G57" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="H57" s="3">
-        <v>14700</v>
+        <v>14900</v>
       </c>
       <c r="I57" s="3">
-        <v>14100</v>
+        <v>14200</v>
       </c>
       <c r="J57" s="3">
         <v>3600</v>
@@ -2575,10 +2575,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22300</v>
+        <v>22500</v>
       </c>
       <c r="E58" s="3">
-        <v>22000</v>
+        <v>22200</v>
       </c>
       <c r="F58" s="3">
         <v>4200</v>
@@ -2587,13 +2587,13 @@
         <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>130200</v>
+        <v>131500</v>
       </c>
       <c r="I58" s="3">
-        <v>36700</v>
+        <v>37100</v>
       </c>
       <c r="J58" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2617,19 +2617,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>36900</v>
+        <v>37200</v>
       </c>
       <c r="E59" s="3">
-        <v>36000</v>
+        <v>36300</v>
       </c>
       <c r="F59" s="3">
-        <v>40800</v>
+        <v>41200</v>
       </c>
       <c r="G59" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="H59" s="3">
-        <v>51300</v>
+        <v>51800</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2659,25 +2659,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>75200</v>
+        <v>75900</v>
       </c>
       <c r="E60" s="3">
-        <v>65100</v>
+        <v>65800</v>
       </c>
       <c r="F60" s="3">
-        <v>48000</v>
+        <v>48500</v>
       </c>
       <c r="G60" s="3">
-        <v>17600</v>
+        <v>17800</v>
       </c>
       <c r="H60" s="3">
-        <v>196200</v>
+        <v>198200</v>
       </c>
       <c r="I60" s="3">
-        <v>50800</v>
+        <v>51300</v>
       </c>
       <c r="J60" s="3">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="K60" s="3">
         <v>800</v>
@@ -2701,22 +2701,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>99500</v>
+        <v>100500</v>
       </c>
       <c r="E61" s="3">
-        <v>101800</v>
+        <v>102800</v>
       </c>
       <c r="F61" s="3">
-        <v>20200</v>
+        <v>20400</v>
       </c>
       <c r="G61" s="3">
         <v>800</v>
       </c>
       <c r="H61" s="3">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="I61" s="3">
-        <v>35300</v>
+        <v>35700</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
@@ -2743,7 +2743,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E62" s="3">
         <v>2000</v>
@@ -2911,25 +2911,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>190300</v>
+        <v>192200</v>
       </c>
       <c r="E66" s="3">
-        <v>184300</v>
+        <v>186100</v>
       </c>
       <c r="F66" s="3">
-        <v>71700</v>
+        <v>72400</v>
       </c>
       <c r="G66" s="3">
-        <v>21600</v>
+        <v>21800</v>
       </c>
       <c r="H66" s="3">
-        <v>213900</v>
+        <v>216100</v>
       </c>
       <c r="I66" s="3">
-        <v>86100</v>
+        <v>86900</v>
       </c>
       <c r="J66" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="K66" s="3">
         <v>800</v>
@@ -3139,25 +3139,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-917200</v>
+        <v>-926500</v>
       </c>
       <c r="E72" s="3">
-        <v>-794200</v>
+        <v>-802200</v>
       </c>
       <c r="F72" s="3">
-        <v>-566300</v>
+        <v>-572000</v>
       </c>
       <c r="G72" s="3">
-        <v>-407000</v>
+        <v>-411100</v>
       </c>
       <c r="H72" s="3">
-        <v>-242300</v>
+        <v>-244800</v>
       </c>
       <c r="I72" s="3">
-        <v>-62500</v>
+        <v>-63100</v>
       </c>
       <c r="J72" s="3">
-        <v>-12100</v>
+        <v>-12200</v>
       </c>
       <c r="K72" s="3">
         <v>-2700</v>
@@ -3307,25 +3307,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>883300</v>
+        <v>892200</v>
       </c>
       <c r="E76" s="3">
-        <v>952100</v>
+        <v>961700</v>
       </c>
       <c r="F76" s="3">
-        <v>968700</v>
+        <v>978500</v>
       </c>
       <c r="G76" s="3">
-        <v>193300</v>
+        <v>195200</v>
       </c>
       <c r="H76" s="3">
-        <v>157800</v>
+        <v>159400</v>
       </c>
       <c r="I76" s="3">
         <v>-5800</v>
       </c>
       <c r="J76" s="3">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="K76" s="3">
         <v>8500</v>
@@ -3438,25 +3438,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-125800</v>
+        <v>-127100</v>
       </c>
       <c r="E81" s="3">
-        <v>-244200</v>
+        <v>-246700</v>
       </c>
       <c r="F81" s="3">
-        <v>-165400</v>
+        <v>-167100</v>
       </c>
       <c r="G81" s="3">
-        <v>-170000</v>
+        <v>-171700</v>
       </c>
       <c r="H81" s="3">
-        <v>-197800</v>
+        <v>-199800</v>
       </c>
       <c r="I81" s="3">
-        <v>-41200</v>
+        <v>-41600</v>
       </c>
       <c r="J81" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="K81" s="3">
         <v>-1100</v>
@@ -3498,19 +3498,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>47300</v>
+        <v>47800</v>
       </c>
       <c r="E83" s="3">
-        <v>34500</v>
+        <v>34800</v>
       </c>
       <c r="F83" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="G83" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="H83" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
@@ -3750,25 +3750,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12100</v>
+        <v>-12300</v>
       </c>
       <c r="E89" s="3">
         <v>-4900</v>
       </c>
       <c r="F89" s="3">
-        <v>-113500</v>
+        <v>-114700</v>
       </c>
       <c r="G89" s="3">
-        <v>-41900</v>
+        <v>-42300</v>
       </c>
       <c r="H89" s="3">
-        <v>-82200</v>
+        <v>-83000</v>
       </c>
       <c r="I89" s="3">
-        <v>-18500</v>
+        <v>-18700</v>
       </c>
       <c r="J89" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="K89" s="3">
         <v>-1000</v>
@@ -3810,10 +3810,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="E91" s="3">
-        <v>-7800</v>
+        <v>-7900</v>
       </c>
       <c r="F91" s="3">
         <v>-2800</v>
@@ -3822,13 +3822,13 @@
         <v>-2200</v>
       </c>
       <c r="H91" s="3">
-        <v>-100700</v>
+        <v>-101700</v>
       </c>
       <c r="I91" s="3">
-        <v>-55600</v>
+        <v>-56200</v>
       </c>
       <c r="J91" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="K91" s="3">
         <v>-3500</v>
@@ -3936,22 +3936,22 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-18100</v>
+        <v>-18300</v>
       </c>
       <c r="E94" s="3">
-        <v>-167700</v>
+        <v>-169400</v>
       </c>
       <c r="F94" s="3">
-        <v>-361700</v>
+        <v>-365300</v>
       </c>
       <c r="G94" s="3">
-        <v>-51700</v>
+        <v>-52200</v>
       </c>
       <c r="H94" s="3">
-        <v>-155300</v>
+        <v>-156900</v>
       </c>
       <c r="I94" s="3">
-        <v>-48100</v>
+        <v>-48600</v>
       </c>
       <c r="J94" s="3">
         <v>-7100</v>
@@ -4164,25 +4164,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-31400</v>
+        <v>-31700</v>
       </c>
       <c r="E100" s="3">
-        <v>-30500</v>
+        <v>-30800</v>
       </c>
       <c r="F100" s="3">
-        <v>838000</v>
+        <v>846500</v>
       </c>
       <c r="G100" s="3">
-        <v>104000</v>
+        <v>105100</v>
       </c>
       <c r="H100" s="3">
-        <v>261100</v>
+        <v>263700</v>
       </c>
       <c r="I100" s="3">
-        <v>71300</v>
+        <v>72100</v>
       </c>
       <c r="J100" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="K100" s="3">
         <v>6500</v>
@@ -4248,19 +4248,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-61600</v>
+        <v>-62200</v>
       </c>
       <c r="E102" s="3">
-        <v>-203100</v>
+        <v>-205100</v>
       </c>
       <c r="F102" s="3">
-        <v>362800</v>
+        <v>366500</v>
       </c>
       <c r="G102" s="3">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="H102" s="3">
-        <v>22700</v>
+        <v>23000</v>
       </c>
       <c r="I102" s="3">
         <v>4700</v>

--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>SNDL</t>
   </si>
@@ -725,19 +725,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>669100</v>
+        <v>688300</v>
       </c>
       <c r="E8" s="3">
-        <v>524300</v>
+        <v>526200</v>
       </c>
       <c r="F8" s="3">
-        <v>41300</v>
+        <v>44400</v>
       </c>
       <c r="G8" s="3">
-        <v>44800</v>
+        <v>47800</v>
       </c>
       <c r="H8" s="3">
-        <v>46800</v>
+        <v>49000</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -767,25 +767,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>507400</v>
+        <v>544100</v>
       </c>
       <c r="E9" s="3">
-        <v>410800</v>
+        <v>422500</v>
       </c>
       <c r="F9" s="3">
-        <v>37300</v>
+        <v>51500</v>
       </c>
       <c r="G9" s="3">
-        <v>38100</v>
+        <v>86900</v>
       </c>
       <c r="H9" s="3">
-        <v>34400</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>20900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -809,25 +809,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>161700</v>
+        <v>144200</v>
       </c>
       <c r="E10" s="3">
-        <v>113400</v>
+        <v>103700</v>
       </c>
       <c r="F10" s="3">
-        <v>4100</v>
+        <v>-7100</v>
       </c>
       <c r="G10" s="3">
-        <v>6800</v>
+        <v>-39100</v>
       </c>
       <c r="H10" s="3">
-        <v>12400</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>28100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -875,13 +875,13 @@
         <v>1800</v>
       </c>
       <c r="F12" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="G12" s="3">
         <v>400</v>
       </c>
       <c r="H12" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
@@ -953,25 +953,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>86000</v>
+        <v>69000</v>
       </c>
       <c r="E14" s="3">
-        <v>150900</v>
+        <v>220000</v>
       </c>
       <c r="F14" s="3">
-        <v>65300</v>
+        <v>89500</v>
       </c>
       <c r="G14" s="3">
-        <v>92500</v>
+        <v>65500</v>
       </c>
       <c r="H14" s="3">
-        <v>102200</v>
+        <v>46600</v>
       </c>
       <c r="I14" s="3">
-        <v>1300</v>
+        <v>20200</v>
       </c>
       <c r="J14" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -995,22 +995,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>44300</v>
+        <v>45600</v>
       </c>
       <c r="E15" s="3">
-        <v>30100</v>
+        <v>30300</v>
       </c>
       <c r="F15" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="G15" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="H15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1052,25 +1052,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>802400</v>
+        <v>764300</v>
       </c>
       <c r="E17" s="3">
-        <v>793600</v>
+        <v>571500</v>
       </c>
       <c r="F17" s="3">
-        <v>162800</v>
+        <v>101300</v>
       </c>
       <c r="G17" s="3">
-        <v>184000</v>
+        <v>127400</v>
       </c>
       <c r="H17" s="3">
-        <v>135900</v>
+        <v>89300</v>
       </c>
       <c r="I17" s="3">
-        <v>20400</v>
+        <v>23800</v>
       </c>
       <c r="J17" s="3">
-        <v>9500</v>
+        <v>8400</v>
       </c>
       <c r="K17" s="3">
         <v>1100</v>
@@ -1094,25 +1094,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-133300</v>
+        <v>-75900</v>
       </c>
       <c r="E18" s="3">
-        <v>-269300</v>
+        <v>-45300</v>
       </c>
       <c r="F18" s="3">
-        <v>-121500</v>
+        <v>-57000</v>
       </c>
       <c r="G18" s="3">
-        <v>-139100</v>
+        <v>-79600</v>
       </c>
       <c r="H18" s="3">
-        <v>-89100</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-40300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-8400</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1154,25 +1154,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12500</v>
+        <v>-9100</v>
       </c>
       <c r="E20" s="3">
-        <v>-5900</v>
+        <v>24000</v>
       </c>
       <c r="F20" s="3">
-        <v>-50700</v>
+        <v>49200</v>
       </c>
       <c r="G20" s="3">
-        <v>-5900</v>
+        <v>8400</v>
       </c>
       <c r="H20" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>17400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1196,25 +1196,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-73000</v>
+        <v>-21300</v>
       </c>
       <c r="E21" s="3">
-        <v>-240400</v>
+        <v>-39000</v>
       </c>
       <c r="F21" s="3">
-        <v>-164700</v>
+        <v>-102000</v>
       </c>
       <c r="G21" s="3">
-        <v>-136500</v>
+        <v>-84200</v>
       </c>
       <c r="H21" s="3">
-        <v>-90000</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-57200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-8100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1238,25 +1238,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="E22" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="F22" s="3">
         <v>600</v>
       </c>
       <c r="G22" s="3">
-        <v>6800</v>
+        <v>7200</v>
       </c>
       <c r="H22" s="3">
-        <v>10500</v>
+        <v>7300</v>
       </c>
       <c r="I22" s="3">
-        <v>21200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
+        <v>800</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1280,25 +1280,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-126600</v>
+        <v>-130300</v>
       </c>
       <c r="E23" s="3">
-        <v>-279600</v>
+        <v>-280600</v>
       </c>
       <c r="F23" s="3">
-        <v>-172800</v>
+        <v>-185500</v>
       </c>
       <c r="G23" s="3">
-        <v>-151900</v>
+        <v>-161900</v>
       </c>
       <c r="H23" s="3">
-        <v>-107700</v>
+        <v>-112800</v>
       </c>
       <c r="I23" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="J23" s="3">
-        <v>-9600</v>
+        <v>-10100</v>
       </c>
       <c r="K23" s="3">
         <v>-1100</v>
@@ -1321,20 +1321,20 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>-5400</v>
       </c>
       <c r="F24" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+        <v>-6300</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1406,25 +1406,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-126600</v>
+        <v>-130300</v>
       </c>
       <c r="E26" s="3">
-        <v>-274100</v>
+        <v>-275200</v>
       </c>
       <c r="F26" s="3">
-        <v>-166900</v>
+        <v>-179200</v>
       </c>
       <c r="G26" s="3">
-        <v>-151900</v>
+        <v>-161900</v>
       </c>
       <c r="H26" s="3">
-        <v>-105000</v>
+        <v>-110000</v>
       </c>
       <c r="I26" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="J26" s="3">
-        <v>-9600</v>
+        <v>-10100</v>
       </c>
       <c r="K26" s="3">
         <v>-1100</v>
@@ -1448,25 +1448,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-123800</v>
+        <v>-130700</v>
       </c>
       <c r="E27" s="3">
-        <v>-246700</v>
+        <v>-247600</v>
       </c>
       <c r="F27" s="3">
-        <v>-167100</v>
+        <v>-179400</v>
       </c>
       <c r="G27" s="3">
-        <v>-146900</v>
+        <v>-183100</v>
       </c>
       <c r="H27" s="3">
-        <v>-104900</v>
+        <v>-209300</v>
       </c>
       <c r="I27" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="J27" s="3">
-        <v>-9600</v>
+        <v>-10100</v>
       </c>
       <c r="K27" s="3">
         <v>-1100</v>
@@ -1532,7 +1532,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-3300</v>
+        <v>-3400</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1541,16 +1541,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-24800</v>
+        <v>-26400</v>
       </c>
       <c r="H29" s="3">
-        <v>-94900</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>-99400</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1658,25 +1658,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12500</v>
+        <v>9100</v>
       </c>
       <c r="E32" s="3">
-        <v>5900</v>
+        <v>-24000</v>
       </c>
       <c r="F32" s="3">
-        <v>50700</v>
+        <v>-49200</v>
       </c>
       <c r="G32" s="3">
-        <v>5900</v>
+        <v>-8400</v>
       </c>
       <c r="H32" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-17400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1700,25 +1700,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-127100</v>
+        <v>-130700</v>
       </c>
       <c r="E33" s="3">
-        <v>-246700</v>
+        <v>-247600</v>
       </c>
       <c r="F33" s="3">
-        <v>-167100</v>
+        <v>-179400</v>
       </c>
       <c r="G33" s="3">
-        <v>-171700</v>
+        <v>-183100</v>
       </c>
       <c r="H33" s="3">
-        <v>-199800</v>
+        <v>-209300</v>
       </c>
       <c r="I33" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="J33" s="3">
-        <v>-9600</v>
+        <v>-10100</v>
       </c>
       <c r="K33" s="3">
         <v>-1100</v>
@@ -1784,25 +1784,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-127100</v>
+        <v>-130700</v>
       </c>
       <c r="E35" s="3">
-        <v>-246700</v>
+        <v>-247600</v>
       </c>
       <c r="F35" s="3">
-        <v>-167100</v>
+        <v>-179400</v>
       </c>
       <c r="G35" s="3">
-        <v>-171700</v>
+        <v>-183100</v>
       </c>
       <c r="H35" s="3">
-        <v>-199800</v>
+        <v>-209300</v>
       </c>
       <c r="I35" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="J35" s="3">
-        <v>-9600</v>
+        <v>-10100</v>
       </c>
       <c r="K35" s="3">
         <v>-1100</v>
@@ -1909,25 +1909,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>143600</v>
+        <v>147700</v>
       </c>
       <c r="E41" s="3">
-        <v>205800</v>
+        <v>206600</v>
       </c>
       <c r="F41" s="3">
-        <v>410900</v>
+        <v>441100</v>
       </c>
       <c r="G41" s="3">
-        <v>44400</v>
+        <v>47400</v>
       </c>
       <c r="H41" s="3">
-        <v>33400</v>
+        <v>35000</v>
       </c>
       <c r="I41" s="3">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="J41" s="3">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="K41" s="3">
         <v>2700</v>
@@ -1951,25 +1951,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4900</v>
+        <v>2700</v>
       </c>
       <c r="E42" s="3">
-        <v>23700</v>
+        <v>21000</v>
       </c>
       <c r="F42" s="3">
-        <v>66800</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>68600</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1993,19 +1993,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>19900</v>
+        <v>22700</v>
       </c>
       <c r="E43" s="3">
-        <v>16700</v>
+        <v>19500</v>
       </c>
       <c r="F43" s="3">
-        <v>8000</v>
+        <v>11700</v>
       </c>
       <c r="G43" s="3">
-        <v>11700</v>
+        <v>12500</v>
       </c>
       <c r="H43" s="3">
-        <v>20300</v>
+        <v>21300</v>
       </c>
       <c r="I43" s="3">
         <v>2000</v>
@@ -2035,22 +2035,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>95300</v>
+        <v>98100</v>
       </c>
       <c r="E44" s="3">
-        <v>96600</v>
+        <v>97000</v>
       </c>
       <c r="F44" s="3">
-        <v>44900</v>
+        <v>26800</v>
       </c>
       <c r="G44" s="3">
-        <v>21500</v>
+        <v>22900</v>
       </c>
       <c r="H44" s="3">
-        <v>54700</v>
+        <v>57200</v>
       </c>
       <c r="I44" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
@@ -2077,25 +2077,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>35900</v>
+        <v>4800</v>
       </c>
       <c r="E45" s="3">
-        <v>26400</v>
+        <v>4700</v>
       </c>
       <c r="F45" s="3">
-        <v>25300</v>
+        <v>2400</v>
       </c>
       <c r="G45" s="3">
-        <v>9500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>18700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
+        <v>2400</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
@@ -2119,25 +2119,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>299500</v>
+        <v>308100</v>
       </c>
       <c r="E46" s="3">
-        <v>369100</v>
+        <v>370500</v>
       </c>
       <c r="F46" s="3">
-        <v>536000</v>
+        <v>575400</v>
       </c>
       <c r="G46" s="3">
-        <v>87100</v>
+        <v>92900</v>
       </c>
       <c r="H46" s="3">
-        <v>127100</v>
+        <v>133100</v>
       </c>
       <c r="I46" s="3">
-        <v>16000</v>
+        <v>15900</v>
       </c>
       <c r="J46" s="3">
-        <v>6600</v>
+        <v>7000</v>
       </c>
       <c r="K46" s="3">
         <v>3100</v>
@@ -2161,16 +2161,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>431600</v>
+        <v>430100</v>
       </c>
       <c r="E47" s="3">
-        <v>463400</v>
+        <v>450700</v>
       </c>
       <c r="F47" s="3">
-        <v>372400</v>
+        <v>382000</v>
       </c>
       <c r="G47" s="3">
-        <v>38200</v>
+        <v>40700</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2203,25 +2203,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>208000</v>
+        <v>214000</v>
       </c>
       <c r="E48" s="3">
-        <v>204300</v>
+        <v>205100</v>
       </c>
       <c r="F48" s="3">
-        <v>46500</v>
+        <v>49900</v>
       </c>
       <c r="G48" s="3">
-        <v>86100</v>
+        <v>91800</v>
       </c>
       <c r="H48" s="3">
-        <v>207600</v>
+        <v>217400</v>
       </c>
       <c r="I48" s="3">
-        <v>65100</v>
+        <v>64900</v>
       </c>
       <c r="J48" s="3">
-        <v>9600</v>
+        <v>10200</v>
       </c>
       <c r="K48" s="3">
         <v>5900</v>
@@ -2245,19 +2245,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>141700</v>
+        <v>145700</v>
       </c>
       <c r="E49" s="3">
-        <v>104600</v>
+        <v>105000</v>
       </c>
       <c r="F49" s="3">
-        <v>90300</v>
+        <v>96900</v>
       </c>
       <c r="G49" s="3">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="H49" s="3">
-        <v>40800</v>
+        <v>42700</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2371,25 +2371,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E52" s="3">
         <v>6300</v>
       </c>
       <c r="F52" s="3">
-        <v>5700</v>
+        <v>6100</v>
       </c>
       <c r="G52" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2455,25 +2455,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1084400</v>
+        <v>1115500</v>
       </c>
       <c r="E54" s="3">
-        <v>1147900</v>
+        <v>1152200</v>
       </c>
       <c r="F54" s="3">
-        <v>1050900</v>
+        <v>1128100</v>
       </c>
       <c r="G54" s="3">
-        <v>217100</v>
+        <v>231400</v>
       </c>
       <c r="H54" s="3">
-        <v>375400</v>
+        <v>393200</v>
       </c>
       <c r="I54" s="3">
-        <v>81100</v>
+        <v>80800</v>
       </c>
       <c r="J54" s="3">
-        <v>19000</v>
+        <v>20100</v>
       </c>
       <c r="K54" s="3">
         <v>9400</v>
@@ -2533,25 +2533,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>16200</v>
+        <v>16700</v>
       </c>
       <c r="E57" s="3">
         <v>7200</v>
       </c>
       <c r="F57" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="G57" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="H57" s="3">
-        <v>14900</v>
+        <v>15600</v>
       </c>
       <c r="I57" s="3">
-        <v>14200</v>
+        <v>8100</v>
       </c>
       <c r="J57" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="K57" s="3">
         <v>800</v>
@@ -2575,25 +2575,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22500</v>
+        <v>23100</v>
       </c>
       <c r="E58" s="3">
-        <v>22200</v>
+        <v>22300</v>
       </c>
       <c r="F58" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="G58" s="3">
         <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>131500</v>
+        <v>137700</v>
       </c>
       <c r="I58" s="3">
-        <v>37100</v>
+        <v>35200</v>
       </c>
       <c r="J58" s="3">
-        <v>5200</v>
+        <v>5500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2617,19 +2617,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>37200</v>
+        <v>3300</v>
       </c>
       <c r="E59" s="3">
-        <v>36300</v>
+        <v>8100</v>
       </c>
       <c r="F59" s="3">
-        <v>41200</v>
+        <v>17100</v>
       </c>
       <c r="G59" s="3">
-        <v>13900</v>
+        <v>300</v>
       </c>
       <c r="H59" s="3">
-        <v>51800</v>
+        <v>25100</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2659,25 +2659,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>75900</v>
+        <v>78100</v>
       </c>
       <c r="E60" s="3">
-        <v>65800</v>
+        <v>66000</v>
       </c>
       <c r="F60" s="3">
-        <v>48500</v>
+        <v>52000</v>
       </c>
       <c r="G60" s="3">
-        <v>17800</v>
+        <v>18900</v>
       </c>
       <c r="H60" s="3">
-        <v>198200</v>
+        <v>207600</v>
       </c>
       <c r="I60" s="3">
-        <v>51300</v>
+        <v>51000</v>
       </c>
       <c r="J60" s="3">
-        <v>8800</v>
+        <v>9300</v>
       </c>
       <c r="K60" s="3">
         <v>800</v>
@@ -2701,22 +2701,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100500</v>
+        <v>103400</v>
       </c>
       <c r="E61" s="3">
-        <v>102800</v>
+        <v>103200</v>
       </c>
       <c r="F61" s="3">
-        <v>20400</v>
+        <v>21900</v>
       </c>
       <c r="G61" s="3">
         <v>800</v>
       </c>
       <c r="H61" s="3">
-        <v>11900</v>
+        <v>12500</v>
       </c>
       <c r="I61" s="3">
-        <v>35700</v>
+        <v>23700</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
@@ -2743,22 +2743,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="E62" s="3">
         <v>2000</v>
       </c>
       <c r="F62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+        <v>3600</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>11800</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2911,25 +2911,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>192200</v>
+        <v>184600</v>
       </c>
       <c r="E66" s="3">
-        <v>186100</v>
+        <v>171200</v>
       </c>
       <c r="F66" s="3">
-        <v>72400</v>
+        <v>77500</v>
       </c>
       <c r="G66" s="3">
-        <v>21800</v>
+        <v>19800</v>
       </c>
       <c r="H66" s="3">
-        <v>216100</v>
+        <v>222700</v>
       </c>
       <c r="I66" s="3">
-        <v>86900</v>
+        <v>86600</v>
       </c>
       <c r="J66" s="3">
-        <v>8900</v>
+        <v>9400</v>
       </c>
       <c r="K66" s="3">
         <v>800</v>
@@ -3139,25 +3139,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-926500</v>
+        <v>-954700</v>
       </c>
       <c r="E72" s="3">
-        <v>-802200</v>
+        <v>-806800</v>
       </c>
       <c r="F72" s="3">
-        <v>-572000</v>
+        <v>-620400</v>
       </c>
       <c r="G72" s="3">
-        <v>-411100</v>
+        <v>-438000</v>
       </c>
       <c r="H72" s="3">
-        <v>-244800</v>
+        <v>-277800</v>
       </c>
       <c r="I72" s="3">
-        <v>-63100</v>
+        <v>-65100</v>
       </c>
       <c r="J72" s="3">
-        <v>-12200</v>
+        <v>-13000</v>
       </c>
       <c r="K72" s="3">
         <v>-2700</v>
@@ -3307,25 +3307,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>892200</v>
+        <v>917800</v>
       </c>
       <c r="E76" s="3">
-        <v>961700</v>
+        <v>965300</v>
       </c>
       <c r="F76" s="3">
-        <v>978500</v>
+        <v>1050400</v>
       </c>
       <c r="G76" s="3">
-        <v>195200</v>
+        <v>213200</v>
       </c>
       <c r="H76" s="3">
-        <v>159400</v>
+        <v>166900</v>
       </c>
       <c r="I76" s="3">
         <v>-5800</v>
       </c>
       <c r="J76" s="3">
-        <v>10100</v>
+        <v>10700</v>
       </c>
       <c r="K76" s="3">
         <v>8500</v>
@@ -3438,25 +3438,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-127100</v>
+        <v>-130700</v>
       </c>
       <c r="E81" s="3">
-        <v>-246700</v>
+        <v>-247600</v>
       </c>
       <c r="F81" s="3">
-        <v>-167100</v>
+        <v>-179400</v>
       </c>
       <c r="G81" s="3">
-        <v>-171700</v>
+        <v>-183100</v>
       </c>
       <c r="H81" s="3">
-        <v>-199800</v>
+        <v>-209300</v>
       </c>
       <c r="I81" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="J81" s="3">
-        <v>-9600</v>
+        <v>-10100</v>
       </c>
       <c r="K81" s="3">
         <v>-1100</v>
@@ -3498,22 +3498,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>47800</v>
+        <v>47400</v>
       </c>
       <c r="E83" s="3">
-        <v>34800</v>
+        <v>33300</v>
       </c>
       <c r="F83" s="3">
-        <v>7500</v>
+        <v>7300</v>
       </c>
       <c r="G83" s="3">
-        <v>8500</v>
+        <v>9100</v>
       </c>
       <c r="H83" s="3">
-        <v>7200</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
@@ -3750,25 +3750,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12300</v>
+        <v>-12600</v>
       </c>
       <c r="E89" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="F89" s="3">
-        <v>-114700</v>
+        <v>-123100</v>
       </c>
       <c r="G89" s="3">
-        <v>-42300</v>
+        <v>-45100</v>
       </c>
       <c r="H89" s="3">
-        <v>-83000</v>
+        <v>-86900</v>
       </c>
       <c r="I89" s="3">
-        <v>-18700</v>
+        <v>-18900</v>
       </c>
       <c r="J89" s="3">
-        <v>-3900</v>
+        <v>-4100</v>
       </c>
       <c r="K89" s="3">
         <v>-1000</v>
@@ -3810,25 +3810,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="E91" s="3">
         <v>-7900</v>
       </c>
       <c r="F91" s="3">
-        <v>-2800</v>
+        <v>-3000</v>
       </c>
       <c r="G91" s="3">
-        <v>-2200</v>
+        <v>-2400</v>
       </c>
       <c r="H91" s="3">
-        <v>-101700</v>
+        <v>-85000</v>
       </c>
       <c r="I91" s="3">
-        <v>-56200</v>
+        <v>-55900</v>
       </c>
       <c r="J91" s="3">
-        <v>-5600</v>
+        <v>-5900</v>
       </c>
       <c r="K91" s="3">
         <v>-3500</v>
@@ -3936,25 +3936,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-18300</v>
+        <v>-18800</v>
       </c>
       <c r="E94" s="3">
-        <v>-169400</v>
+        <v>-170100</v>
       </c>
       <c r="F94" s="3">
-        <v>-365300</v>
+        <v>-392200</v>
       </c>
       <c r="G94" s="3">
-        <v>-52200</v>
+        <v>-55600</v>
       </c>
       <c r="H94" s="3">
-        <v>-156900</v>
+        <v>-164300</v>
       </c>
       <c r="I94" s="3">
-        <v>-48600</v>
+        <v>-48400</v>
       </c>
       <c r="J94" s="3">
-        <v>-7100</v>
+        <v>-7600</v>
       </c>
       <c r="K94" s="3">
         <v>-2900</v>
@@ -4164,25 +4164,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-31700</v>
+        <v>-32600</v>
       </c>
       <c r="E100" s="3">
-        <v>-30800</v>
+        <v>-30900</v>
       </c>
       <c r="F100" s="3">
-        <v>846500</v>
+        <v>908700</v>
       </c>
       <c r="G100" s="3">
-        <v>105100</v>
+        <v>112000</v>
       </c>
       <c r="H100" s="3">
-        <v>263700</v>
+        <v>276200</v>
       </c>
       <c r="I100" s="3">
-        <v>72100</v>
+        <v>86400</v>
       </c>
       <c r="J100" s="3">
-        <v>13900</v>
+        <v>14700</v>
       </c>
       <c r="K100" s="3">
         <v>6500</v>
@@ -4248,25 +4248,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-62200</v>
+        <v>-64000</v>
       </c>
       <c r="E102" s="3">
-        <v>-205100</v>
+        <v>-205900</v>
       </c>
       <c r="F102" s="3">
-        <v>366500</v>
+        <v>393400</v>
       </c>
       <c r="G102" s="3">
-        <v>11100</v>
+        <v>11800</v>
       </c>
       <c r="H102" s="3">
-        <v>23000</v>
+        <v>24100</v>
       </c>
       <c r="I102" s="3">
-        <v>4700</v>
+        <v>19100</v>
       </c>
       <c r="J102" s="3">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="K102" s="3">
         <v>2500</v>

--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>SNDL</t>
   </si>
@@ -656,59 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43159</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42794</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,30 +718,33 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>639700</v>
+      </c>
+      <c r="E8" s="3">
         <v>688300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>526200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -757,39 +760,42 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>472700</v>
+      </c>
+      <c r="E9" s="3">
         <v>544100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>422500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>86900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -802,36 +808,39 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E10" s="3">
         <v>144200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>103700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-7100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-39100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-5700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,26 +885,26 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,38 +962,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E14" s="3">
         <v>69000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>220000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>89500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>65500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>46600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>20200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -988,39 +1007,42 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E15" s="3">
         <v>45600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>30300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,9 +1052,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,38 +1071,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>663000</v>
+      </c>
+      <c r="E17" s="3">
         <v>764300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>571500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>101300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>127400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>89300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,36 +1113,39 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-75900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-45300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-57000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-79600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-40300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1129,9 +1158,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,35 +1180,36 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>24000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>49200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,36 +1222,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-39000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-102000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-84200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-57200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,38 +1267,41 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>6000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1273,39 +1312,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-130300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-280600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-185500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-161900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-112800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,30 +1357,33 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6300</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-2800</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1354,12 +1399,15 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,39 +1447,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-130300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-275200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-179200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-161900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-110000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,39 +1492,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-130700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-247600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-179400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-183100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-209300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,9 +1537,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,35 +1582,38 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-3400</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-26400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-99400</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1561,15 +1621,18 @@
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,36 +1717,39 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E32" s="3">
         <v>9100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-24000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-49200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1693,39 +1762,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-130700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-247600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-179400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-183100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-209300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,9 +1807,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,39 +1852,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-130700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-247600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-179400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-183100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-209300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,44 +1897,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43159</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42794</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1866,9 +1947,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,38 +1988,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>151800</v>
+      </c>
+      <c r="E41" s="3">
         <v>147700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>206600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>441100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>47400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2700</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,24 +2030,27 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>68600</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1971,14 +2060,14 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1986,39 +2075,42 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E43" s="3">
         <v>22700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,38 +2120,41 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E44" s="3">
         <v>98100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>97000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>57200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2070,26 +2165,29 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2400</v>
       </c>
       <c r="G45" s="3">
         <v>2400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>2400</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -2097,12 +2195,12 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2112,39 +2210,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E46" s="3">
         <v>308100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>370500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>575400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>92900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>133100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2154,27 +2255,30 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E47" s="3">
         <v>430100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>450700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>382000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40700</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2190,45 +2294,48 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>181600</v>
+      </c>
+      <c r="E48" s="3">
         <v>214000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>205100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>49900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>91800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>217400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2238,38 +2345,41 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E49" s="3">
         <v>145700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>105000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>96900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42700</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>400</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>400</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,38 +2480,41 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>3700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2406,9 +2525,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,39 +2570,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>937700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1115500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1152200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1128100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>231400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>393200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>80800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,9 +2615,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,38 +2656,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E57" s="3">
         <v>16700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2568,38 +2698,41 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E58" s="3">
         <v>23100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>137700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2610,30 +2743,33 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>3300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,42 +2785,45 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E60" s="3">
         <v>78100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>66000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>52000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>207600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,36 +2833,39 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E61" s="3">
         <v>103400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>103200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2736,33 +2878,36 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E62" s="3">
         <v>3200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>11800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2775,12 +2920,15 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,39 +3058,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E66" s="3">
         <v>184600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>171200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>222700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2946,9 +3103,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,39 +3302,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-920200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-954700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-806800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-620400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-438000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-277800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-65100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,9 +3347,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,39 +3482,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>787700</v>
+      </c>
+      <c r="E76" s="3">
         <v>917800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>965300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1050400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>213200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>166900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-5800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3342,9 +3527,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,44 +3572,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43159</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42794</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3431,39 +3622,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-130700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-247600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-179400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-183100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-209300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,9 +3667,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,38 +3689,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E83" s="3">
         <v>47400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,9 +3731,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,39 +3956,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-123100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-45100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-86900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3785,9 +4001,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,38 +4023,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-85000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,9 +4065,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,39 +4155,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-170100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-392200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-55600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-164300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-48400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3971,9 +4200,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,39 +4399,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-32600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>908700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>112000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>276200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>86400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,9 +4444,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4211,18 +4459,18 @@
       <c r="E101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4238,42 +4486,45 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-64000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-205900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>393400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,7 +4534,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>SNDL</t>
   </si>
@@ -972,10 +972,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>14100</v>
+        <v>13500</v>
       </c>
       <c r="E14" s="3">
-        <v>69000</v>
+        <v>62000</v>
       </c>
       <c r="F14" s="3">
         <v>220000</v>
@@ -1187,7 +1187,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>46700</v>
+        <v>42600</v>
       </c>
       <c r="E20" s="3">
         <v>-9100</v>
@@ -1232,7 +1232,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-32400</v>
+        <v>-28200</v>
       </c>
       <c r="E21" s="3">
         <v>-21300</v>
@@ -1276,8 +1276,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>5300</v>
       </c>
       <c r="E22" s="3">
         <v>6000</v>
@@ -1727,7 +1727,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-46700</v>
+        <v>-42600</v>
       </c>
       <c r="E32" s="3">
         <v>9100</v>
@@ -2663,7 +2663,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>39100</v>
+        <v>18800</v>
       </c>
       <c r="E57" s="3">
         <v>16700</v>
@@ -3696,7 +3696,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>39400</v>
+        <v>37600</v>
       </c>
       <c r="E83" s="3">
         <v>47400</v>

--- a/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNDL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>SNDL</t>
   </si>
@@ -656,62 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43159</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42794</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,33 +721,36 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>690200</v>
+      </c>
+      <c r="E8" s="3">
         <v>639700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>688300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>526200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>47800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -763,42 +766,45 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>501600</v>
+      </c>
+      <c r="E9" s="3">
         <v>472700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>544100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>422500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>86900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,39 +817,42 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>188600</v>
+      </c>
+      <c r="E10" s="3">
         <v>167000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>144200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>103700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-7100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-39100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-5700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,38 +888,39 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E12" s="3">
         <v>200</v>
       </c>
       <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
         <v>1800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,41 +981,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E14" s="3">
         <v>13500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>62000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>220000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>89500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>65500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>46600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>20200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1010,42 +1029,45 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E15" s="3">
         <v>37700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>45600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,41 +1097,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>693500</v>
+      </c>
+      <c r="E17" s="3">
         <v>663000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>764300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>571500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>101300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>127400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>89300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,39 +1142,42 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-75900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-45300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-57000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-79600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-40300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,9 +1190,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,38 +1213,39 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>42600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>24000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>49200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,39 +1258,42 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-28200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-39000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-102000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-84200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-57200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-19500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,41 +1306,44 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E22" s="3">
         <v>5300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1315,42 +1354,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-73400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-130300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-280600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-185500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-161900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-112800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,33 +1402,36 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6500</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>-5400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6300</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>-2800</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1402,12 +1447,15 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,42 +1498,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-66900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-130300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-275200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-179200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-161900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-110000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,42 +1546,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-65900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-130700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-247600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-179400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-183100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-209300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,9 +1594,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1595,28 +1655,28 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-3400</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-26400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-99400</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1624,15 +1684,18 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,39 +1786,42 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-42600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-24000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-49200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,42 +1834,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-65900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-130700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-247600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-179400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-183100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-209300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,9 +1882,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,42 +1930,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-65900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-130700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-247600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-179400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-183100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-209300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1900,47 +1978,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43159</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42794</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1950,9 +2031,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,41 +2074,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E41" s="3">
         <v>151800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>147700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>206600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>441100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,27 +2119,30 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>400</v>
+      </c>
+      <c r="E42" s="3">
         <v>19300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>68600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2063,14 +2152,14 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2078,42 +2167,45 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E43" s="3">
         <v>21500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>22700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,41 +2215,44 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E44" s="3">
         <v>89700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>98100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>97000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>57200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
@@ -2168,29 +2263,32 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>13200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2400</v>
       </c>
       <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>2400</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2198,12 +2296,12 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2213,42 +2311,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>327900</v>
+      </c>
+      <c r="E46" s="3">
         <v>321000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>308100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>370500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>575400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>92900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>133100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2258,30 +2359,33 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>289600</v>
+      </c>
+      <c r="E47" s="3">
         <v>293000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>430100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>450700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>382000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2297,48 +2401,51 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E48" s="3">
         <v>181600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>214000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>205100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>217400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>64900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2348,41 +2455,44 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E49" s="3">
         <v>129000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>145700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>105000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>96900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>400</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2393,9 +2503,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,41 +2599,44 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2528,9 +2647,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,42 +2695,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>974300</v>
+      </c>
+      <c r="E54" s="3">
         <v>937700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1115500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1152200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1128100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>231400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>393200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>80800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,9 +2743,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,41 +2786,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E57" s="3">
         <v>18800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,41 +2831,44 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E58" s="3">
         <v>23800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>137700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2746,33 +2879,36 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2788,45 +2924,48 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E60" s="3">
         <v>62900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>78100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>66000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>52000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>207600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,39 +2975,42 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E61" s="3">
         <v>82000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>103400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>103200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2881,36 +3023,39 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E62" s="3">
         <v>5100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>11800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,12 +3068,15 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,42 +3215,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>171200</v>
+      </c>
+      <c r="E66" s="3">
         <v>150000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>184600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>171200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>77500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>222700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>86600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,9 +3263,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,42 +3475,45 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-949900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-920200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-954700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-806800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-620400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-438000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-277800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-65100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2700</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,9 +3523,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,42 +3667,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>803100</v>
+      </c>
+      <c r="E76" s="3">
         <v>787700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>917800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>965300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1050400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>213200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>166900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-5800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,9 +3715,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,47 +3763,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43159</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42794</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3625,42 +3816,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-65900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-130700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-247600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-179400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-183100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-209300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,9 +3864,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,41 +3887,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E83" s="3">
         <v>37600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>47400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,9 +3932,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,42 +4172,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E89" s="3">
         <v>38200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-123100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-45100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-86900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,9 +4220,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,41 +4243,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-85000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,9 +4288,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,42 +4384,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E94" s="3">
         <v>12300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-170100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-392200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-55600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-164300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-48400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,9 +4432,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,42 +4644,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-34300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-32600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>908700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>112000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>276200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>86400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,9 +4692,12 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4462,18 +4710,18 @@
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-900</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4489,45 +4737,48 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E102" s="3">
         <v>16200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-64000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-205900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>393400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>24100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4788,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
